--- a/DBs/wnba/Results/WNBA_2021_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2021_Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerSports\WNBA_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A2DB13-E102-4EEA-BF99-1B56DA90C876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70DB481-7C51-46E1-ABB2-4F521C0C94FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t>H</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -12853,10 +12856,10 @@
         <v>2021</v>
       </c>
       <c r="C386" t="s">
-        <v>10</v>
-      </c>
-      <c r="D386" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D386">
+        <v>0.5</v>
       </c>
       <c r="E386" t="s">
         <v>22</v>
@@ -12885,10 +12888,10 @@
         <v>2021</v>
       </c>
       <c r="C387" t="s">
-        <v>10</v>
-      </c>
-      <c r="D387" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D387">
+        <v>0.5</v>
       </c>
       <c r="E387" t="s">
         <v>20</v>
@@ -12917,10 +12920,10 @@
         <v>2021</v>
       </c>
       <c r="C388" t="s">
-        <v>10</v>
-      </c>
-      <c r="D388" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D388">
+        <v>0.5</v>
       </c>
       <c r="E388" t="s">
         <v>13</v>
@@ -12949,10 +12952,10 @@
         <v>2021</v>
       </c>
       <c r="C389" t="s">
-        <v>10</v>
-      </c>
-      <c r="D389" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D389">
+        <v>0.5</v>
       </c>
       <c r="E389" t="s">
         <v>14</v>
@@ -12981,10 +12984,10 @@
         <v>2021</v>
       </c>
       <c r="C390" t="s">
-        <v>10</v>
-      </c>
-      <c r="D390" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D390">
+        <v>1</v>
       </c>
       <c r="E390" t="s">
         <v>20</v>
@@ -13013,10 +13016,10 @@
         <v>2021</v>
       </c>
       <c r="C391" t="s">
-        <v>10</v>
-      </c>
-      <c r="D391" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D391">
+        <v>1</v>
       </c>
       <c r="E391" t="s">
         <v>16</v>
@@ -13045,10 +13048,10 @@
         <v>2021</v>
       </c>
       <c r="C392" t="s">
-        <v>10</v>
-      </c>
-      <c r="D392" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D392">
+        <v>1</v>
       </c>
       <c r="E392" t="s">
         <v>14</v>
@@ -13077,10 +13080,10 @@
         <v>2021</v>
       </c>
       <c r="C393" t="s">
-        <v>10</v>
-      </c>
-      <c r="D393" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D393">
+        <v>1</v>
       </c>
       <c r="E393" t="s">
         <v>17</v>
@@ -13109,10 +13112,10 @@
         <v>2021</v>
       </c>
       <c r="C394" t="s">
-        <v>10</v>
-      </c>
-      <c r="D394" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D394">
+        <v>2</v>
       </c>
       <c r="E394" t="s">
         <v>20</v>
@@ -13141,10 +13144,10 @@
         <v>2021</v>
       </c>
       <c r="C395" t="s">
-        <v>10</v>
-      </c>
-      <c r="D395" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D395">
+        <v>2</v>
       </c>
       <c r="E395" t="s">
         <v>19</v>
@@ -13173,10 +13176,10 @@
         <v>2021</v>
       </c>
       <c r="C396" t="s">
-        <v>10</v>
-      </c>
-      <c r="D396" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D396">
+        <v>2</v>
       </c>
       <c r="E396" t="s">
         <v>14</v>
@@ -13205,10 +13208,10 @@
         <v>2021</v>
       </c>
       <c r="C397" t="s">
-        <v>10</v>
-      </c>
-      <c r="D397" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D397">
+        <v>2</v>
       </c>
       <c r="E397" t="s">
         <v>23</v>
@@ -13237,10 +13240,10 @@
         <v>2021</v>
       </c>
       <c r="C398" t="s">
-        <v>10</v>
-      </c>
-      <c r="D398" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D398">
+        <v>2</v>
       </c>
       <c r="E398" t="s">
         <v>20</v>
@@ -13269,10 +13272,10 @@
         <v>2021</v>
       </c>
       <c r="C399" t="s">
-        <v>10</v>
-      </c>
-      <c r="D399" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D399">
+        <v>2</v>
       </c>
       <c r="E399" t="s">
         <v>19</v>
@@ -13301,10 +13304,10 @@
         <v>2021</v>
       </c>
       <c r="C400" t="s">
-        <v>10</v>
-      </c>
-      <c r="D400" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D400">
+        <v>2</v>
       </c>
       <c r="E400" t="s">
         <v>14</v>
@@ -13333,10 +13336,10 @@
         <v>2021</v>
       </c>
       <c r="C401" t="s">
-        <v>10</v>
-      </c>
-      <c r="D401" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D401">
+        <v>2</v>
       </c>
       <c r="E401" t="s">
         <v>23</v>
@@ -13365,10 +13368,10 @@
         <v>2021</v>
       </c>
       <c r="C402" t="s">
-        <v>10</v>
-      </c>
-      <c r="D402" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D402">
+        <v>2</v>
       </c>
       <c r="E402" t="s">
         <v>19</v>
@@ -13397,10 +13400,10 @@
         <v>2021</v>
       </c>
       <c r="C403" t="s">
-        <v>10</v>
-      </c>
-      <c r="D403" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D403">
+        <v>2</v>
       </c>
       <c r="E403" t="s">
         <v>20</v>
@@ -13429,10 +13432,10 @@
         <v>2021</v>
       </c>
       <c r="C404" t="s">
-        <v>10</v>
-      </c>
-      <c r="D404" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D404">
+        <v>2</v>
       </c>
       <c r="E404" t="s">
         <v>23</v>
@@ -13461,10 +13464,10 @@
         <v>2021</v>
       </c>
       <c r="C405" t="s">
-        <v>10</v>
-      </c>
-      <c r="D405" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D405">
+        <v>2</v>
       </c>
       <c r="E405" t="s">
         <v>14</v>
@@ -13493,10 +13496,10 @@
         <v>2021</v>
       </c>
       <c r="C406" t="s">
-        <v>10</v>
-      </c>
-      <c r="D406" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D406">
+        <v>2</v>
       </c>
       <c r="E406" t="s">
         <v>19</v>
@@ -13525,10 +13528,10 @@
         <v>2021</v>
       </c>
       <c r="C407" t="s">
-        <v>10</v>
-      </c>
-      <c r="D407" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D407">
+        <v>2</v>
       </c>
       <c r="E407" t="s">
         <v>20</v>
@@ -13557,10 +13560,10 @@
         <v>2021</v>
       </c>
       <c r="C408" t="s">
-        <v>10</v>
-      </c>
-      <c r="D408" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D408">
+        <v>2</v>
       </c>
       <c r="E408" t="s">
         <v>23</v>
@@ -13589,10 +13592,10 @@
         <v>2021</v>
       </c>
       <c r="C409" t="s">
-        <v>10</v>
-      </c>
-      <c r="D409" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D409">
+        <v>2</v>
       </c>
       <c r="E409" t="s">
         <v>14</v>
@@ -13621,10 +13624,10 @@
         <v>2021</v>
       </c>
       <c r="C410" t="s">
-        <v>10</v>
-      </c>
-      <c r="D410" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D410">
+        <v>2</v>
       </c>
       <c r="E410" t="s">
         <v>14</v>
@@ -13653,10 +13656,10 @@
         <v>2021</v>
       </c>
       <c r="C411" t="s">
-        <v>10</v>
-      </c>
-      <c r="D411" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D411">
+        <v>2</v>
       </c>
       <c r="E411" t="s">
         <v>23</v>
@@ -13685,10 +13688,10 @@
         <v>2021</v>
       </c>
       <c r="C412" t="s">
-        <v>10</v>
-      </c>
-      <c r="D412" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D412">
+        <v>3</v>
       </c>
       <c r="E412" t="s">
         <v>20</v>
@@ -13717,10 +13720,10 @@
         <v>2021</v>
       </c>
       <c r="C413" t="s">
-        <v>10</v>
-      </c>
-      <c r="D413" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D413">
+        <v>3</v>
       </c>
       <c r="E413" t="s">
         <v>14</v>
@@ -13749,10 +13752,10 @@
         <v>2021</v>
       </c>
       <c r="C414" t="s">
-        <v>10</v>
-      </c>
-      <c r="D414" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D414">
+        <v>3</v>
       </c>
       <c r="E414" t="s">
         <v>20</v>
@@ -13781,10 +13784,10 @@
         <v>2021</v>
       </c>
       <c r="C415" t="s">
-        <v>10</v>
-      </c>
-      <c r="D415" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D415">
+        <v>3</v>
       </c>
       <c r="E415" t="s">
         <v>14</v>
@@ -13813,10 +13816,10 @@
         <v>2021</v>
       </c>
       <c r="C416" t="s">
-        <v>10</v>
-      </c>
-      <c r="D416" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D416">
+        <v>3</v>
       </c>
       <c r="E416" t="s">
         <v>14</v>
@@ -13845,10 +13848,10 @@
         <v>2021</v>
       </c>
       <c r="C417" t="s">
-        <v>10</v>
-      </c>
-      <c r="D417" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D417">
+        <v>3</v>
       </c>
       <c r="E417" t="s">
         <v>20</v>
@@ -13877,10 +13880,10 @@
         <v>2021</v>
       </c>
       <c r="C418" t="s">
-        <v>10</v>
-      </c>
-      <c r="D418" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D418">
+        <v>3</v>
       </c>
       <c r="E418" t="s">
         <v>14</v>
@@ -13909,10 +13912,10 @@
         <v>2021</v>
       </c>
       <c r="C419" t="s">
-        <v>10</v>
-      </c>
-      <c r="D419" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D419">
+        <v>3</v>
       </c>
       <c r="E419" t="s">
         <v>20</v>
